--- a/Mini Project 2 - Instructor Database.xlsx
+++ b/Mini Project 2 - Instructor Database.xlsx
@@ -1,38 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arun/Desktop/mini-project-2-math-quiz/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90E6203-32BC-0649-AF17-A5B73A3D1A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Challenge-Users" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Timerecord" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Users" sheetId="1" r:id="rId1"/>
+    <sheet name="Questions" sheetId="2" r:id="rId2"/>
+    <sheet name="Challenges" sheetId="3" r:id="rId3"/>
+    <sheet name="Challenge-Users" sheetId="4" r:id="rId4"/>
+    <sheet name="Timerecord" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>challenge_user_id</t>
+  </si>
+  <si>
+    <t>elapsed_time</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>expression</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+  <si>
+    <t>challenge_id</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -51,80 +90,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,74 +392,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>john</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>John Doe</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>jane</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jane Tan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>arun</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Arun Prakash</t>
-        </is>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -488,29 +413,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -519,24 +434,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>question_id</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -545,29 +452,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>challenge_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -576,29 +473,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>challenge_user_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>elapsed_time</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Mini Project 2 - Instructor Database.xlsx
+++ b/Mini Project 2 - Instructor Database.xlsx
@@ -1,77 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arun/Desktop/mini-project-2-math-quiz/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90E6203-32BC-0649-AF17-A5B73A3D1A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="10680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" r:id="rId1"/>
-    <sheet name="Questions" sheetId="2" r:id="rId2"/>
-    <sheet name="Challenges" sheetId="3" r:id="rId3"/>
-    <sheet name="Challenge-Users" sheetId="4" r:id="rId4"/>
-    <sheet name="Timerecord" sheetId="5" r:id="rId5"/>
+    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Challenges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Challenge-Users" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Timerecord" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>challenge_user_id</t>
-  </si>
-  <si>
-    <t>elapsed_time</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>expression</t>
-  </si>
-  <si>
-    <t>answer</t>
-  </si>
-  <si>
-    <t>question_id</t>
-  </si>
-  <si>
-    <t>challenge_id</t>
-  </si>
-  <si>
-    <t>user_id</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -90,21 +50,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -392,19 +411,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tom12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tom Bradley</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jane64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jane Lim</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -413,20 +472,63 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4!3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4!3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(1+2)-(4.3&amp;3)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -434,16 +536,48 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -452,19 +586,62 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>challenge_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -473,19 +650,29 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>challenge_user_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>elapsed_time</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Mini Project 2 - Instructor Database.xlsx
+++ b/Mini Project 2 - Instructor Database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="10680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2120" yWindow="2120" windowWidth="17280" windowHeight="10680" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,20 +429,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
@@ -442,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tom12</t>
+          <t>Limit21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tom Bradley</t>
+          <t>Arun</t>
         </is>
       </c>
     </row>
@@ -457,12 +469,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jane64</t>
+          <t>Aloy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jane Lim</t>
+          <t>Aloysius</t>
         </is>
       </c>
     </row>
@@ -477,21 +489,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>expression</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
@@ -503,10 +515,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4!3</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>uiewdhdiubhcfdewisaniodsw</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -514,21 +525,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4!3</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>(1+2)-(4.3&amp;3)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>(2+2)*3</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -541,16 +543,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>question_id</t>
         </is>
@@ -570,14 +572,6 @@
       </c>
       <c r="B3" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -595,17 +589,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>challenge_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
@@ -638,10 +632,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -655,24 +649,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>challenge_user_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>elapsed_time</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.166797161102295</v>
       </c>
     </row>
   </sheetData>

--- a/Mini Project 2 - Instructor Database.xlsx
+++ b/Mini Project 2 - Instructor Database.xlsx
@@ -1,40 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arun/Desktop/mini-project-2-math-quiz/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A0932F-1116-194B-84F7-9E0FB94FD464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2120" yWindow="2120" windowWidth="17280" windowHeight="10680" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2120" yWindow="2120" windowWidth="17280" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Challenge-Users" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Timerecord" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Users" sheetId="1" r:id="rId1"/>
+    <sheet name="Questions" sheetId="2" r:id="rId2"/>
+    <sheet name="Challenges" sheetId="3" r:id="rId3"/>
+    <sheet name="Challenge-Users" sheetId="4" r:id="rId4"/>
+    <sheet name="Timerecord" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>challenge_user_id</t>
+  </si>
+  <si>
+    <t>elapsed_time</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>expression</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+  <si>
+    <t>challenge_id</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,93 +92,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -423,59 +416,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Limit21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Arun</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Aloy</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Aloysius</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -484,52 +437,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>expression</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>uiewdhdiubhcfdewisaniodsw</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>(2+2)*3</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>12</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -538,40 +458,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>question_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -580,62 +476,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>challenge_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -644,40 +497,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>challenge_user_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>elapsed_time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.166797161102295</v>
       </c>
     </row>
   </sheetData>

--- a/Mini Project 2 - Instructor Database.xlsx
+++ b/Mini Project 2 - Instructor Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arun/Desktop/mini-project-2-math-quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A0932F-1116-194B-84F7-9E0FB94FD464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CB5B59-9FB3-F549-B383-5EB5D8AAF146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2120" yWindow="2120" windowWidth="17280" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,31 +29,31 @@
     <t>id</t>
   </si>
   <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>expression</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+  <si>
+    <t>challenge_id</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
     <t>challenge_user_id</t>
   </si>
   <si>
     <t>elapsed_time</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>expression</t>
-  </si>
-  <si>
-    <t>answer</t>
-  </si>
-  <si>
-    <t>question_id</t>
-  </si>
-  <si>
-    <t>challenge_id</t>
-  </si>
-  <si>
-    <t>user_id</t>
   </si>
 </sst>
 </file>
@@ -72,7 +72,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -425,10 +424,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -446,10 +445,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -467,7 +466,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -485,10 +484,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -506,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
